--- a/input data/care cascade_in.xlsx
+++ b/input data/care cascade_in.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="30326"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="30430"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\chris.seaman\Desktop\GitRepos\burnet-hbv\input data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9CB62381-9DC5-4DD1-839B-198B63A4A1FE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0F1A7638-4C75-4DE5-B076-F9E6791ADB0E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="3660" yWindow="17172" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-19310" yWindow="2330" windowWidth="19420" windowHeight="11500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="inputs" sheetId="2" r:id="rId1"/>
@@ -79,15 +79,21 @@
       <scheme val="minor"/>
     </font>
   </fonts>
-  <fills count="2">
+  <fills count="3">
     <fill>
       <patternFill patternType="none"/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFEEEEEE"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
   </fills>
-  <borders count="1">
+  <borders count="2">
     <border>
       <left/>
       <right/>
@@ -95,15 +101,31 @@
       <bottom/>
       <diagonal/>
     </border>
+    <border>
+      <left style="thin">
+        <color rgb="FFCCCCCC"/>
+      </left>
+      <right style="thin">
+        <color rgb="FFCCCCCC"/>
+      </right>
+      <top style="thin">
+        <color rgb="FFCCCCCC"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FFCCCCCC"/>
+      </bottom>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="9" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="3">
+  <cellXfs count="4">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="10" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="10" fontId="0" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="10" fontId="0" fillId="2" borderId="1" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
   </cellXfs>
   <cellStyles count="2">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -574,53 +596,19 @@
       <c r="B5">
         <v>0</v>
       </c>
-      <c r="C5" s="2">
-        <f>C2-C3</f>
-        <v>0.5282</v>
-      </c>
-      <c r="D5" s="2">
-        <f t="shared" ref="D5:N5" si="0">D2-D3</f>
-        <v>0.50429999999999997</v>
-      </c>
-      <c r="E5" s="2">
-        <f t="shared" si="0"/>
-        <v>0.49869999999999998</v>
-      </c>
-      <c r="F5" s="2">
-        <f t="shared" si="0"/>
-        <v>0.47939999999999999</v>
-      </c>
-      <c r="G5" s="2">
-        <f t="shared" si="0"/>
-        <v>0.46500000000000008</v>
-      </c>
-      <c r="H5" s="2">
-        <f t="shared" si="0"/>
-        <v>0.45130000000000003</v>
-      </c>
-      <c r="I5" s="2">
-        <f t="shared" si="0"/>
-        <v>0.44490000000000002</v>
-      </c>
-      <c r="J5" s="2">
-        <f t="shared" si="0"/>
-        <v>0.46410000000000001</v>
-      </c>
-      <c r="K5" s="2">
-        <f t="shared" si="0"/>
-        <v>0.43469999999999998</v>
-      </c>
-      <c r="L5" s="2">
-        <f t="shared" si="0"/>
-        <v>0.43119999999999997</v>
-      </c>
-      <c r="M5" s="2">
-        <f t="shared" si="0"/>
-        <v>0.40809999999999996</v>
-      </c>
-      <c r="N5" s="2">
-        <f t="shared" si="0"/>
-        <v>0.39479999999999998</v>
+      <c r="C5" s="2"/>
+      <c r="D5" s="2"/>
+      <c r="E5" s="2"/>
+      <c r="F5" s="2"/>
+      <c r="G5" s="2"/>
+      <c r="H5" s="2"/>
+      <c r="I5" s="2"/>
+      <c r="J5" s="2"/>
+      <c r="K5" s="2"/>
+      <c r="L5" s="2"/>
+      <c r="M5" s="2"/>
+      <c r="N5" s="3">
+        <v>0.44761000000000001</v>
       </c>
     </row>
     <row r="6" spans="1:14" x14ac:dyDescent="0.35">
@@ -630,53 +618,19 @@
       <c r="B6">
         <v>0</v>
       </c>
-      <c r="C6" s="2">
-        <f>C3-C4</f>
-        <v>0.12509999999999999</v>
-      </c>
-      <c r="D6" s="2">
-        <f t="shared" ref="D6:N6" si="1">D3-D4</f>
-        <v>0.13600000000000001</v>
-      </c>
-      <c r="E6" s="2">
-        <f t="shared" si="1"/>
-        <v>0.13600000000000001</v>
-      </c>
-      <c r="F6" s="2">
-        <f t="shared" si="1"/>
-        <v>0.14139999999999997</v>
-      </c>
-      <c r="G6" s="2">
-        <f t="shared" si="1"/>
-        <v>0.1416</v>
-      </c>
-      <c r="H6" s="2">
-        <f t="shared" si="1"/>
-        <v>0.14529999999999998</v>
-      </c>
-      <c r="I6" s="2">
-        <f t="shared" si="1"/>
-        <v>0.14109999999999998</v>
-      </c>
-      <c r="J6" s="2">
-        <f t="shared" si="1"/>
-        <v>0.12980000000000003</v>
-      </c>
-      <c r="K6" s="2">
-        <f t="shared" si="1"/>
-        <v>0.16999999999999998</v>
-      </c>
-      <c r="L6" s="2">
-        <f t="shared" si="1"/>
-        <v>0.15799999999999997</v>
-      </c>
-      <c r="M6" s="2">
-        <f t="shared" si="1"/>
-        <v>0.15400000000000003</v>
-      </c>
-      <c r="N6" s="2">
-        <f t="shared" si="1"/>
-        <v>0.1522</v>
+      <c r="C6" s="2"/>
+      <c r="D6" s="2"/>
+      <c r="E6" s="2"/>
+      <c r="F6" s="2"/>
+      <c r="G6" s="2"/>
+      <c r="H6" s="2"/>
+      <c r="I6" s="2"/>
+      <c r="J6" s="2"/>
+      <c r="K6" s="2"/>
+      <c r="L6" s="2"/>
+      <c r="M6" s="2"/>
+      <c r="N6" s="3">
+        <v>0.17107</v>
       </c>
     </row>
     <row r="7" spans="1:14" x14ac:dyDescent="0.35">
@@ -686,53 +640,19 @@
       <c r="B7">
         <v>0</v>
       </c>
-      <c r="C7" s="2">
-        <f>C4</f>
-        <v>6.4899999999999999E-2</v>
-      </c>
-      <c r="D7" s="2">
-        <f t="shared" ref="D7:N7" si="2">D4</f>
-        <v>7.9600000000000004E-2</v>
-      </c>
-      <c r="E7" s="2">
-        <f t="shared" si="2"/>
-        <v>8.6199999999999999E-2</v>
-      </c>
-      <c r="F7" s="2">
-        <f t="shared" si="2"/>
-        <v>9.3100000000000002E-2</v>
-      </c>
-      <c r="G7" s="2">
-        <f t="shared" si="2"/>
-        <v>9.9599999999999994E-2</v>
-      </c>
-      <c r="H7" s="2">
-        <f t="shared" si="2"/>
-        <v>0.10589999999999999</v>
-      </c>
-      <c r="I7" s="2">
-        <f t="shared" si="2"/>
-        <v>0.1116</v>
-      </c>
-      <c r="J7" s="2">
-        <f t="shared" si="2"/>
-        <v>0.1186</v>
-      </c>
-      <c r="K7" s="2">
-        <f t="shared" si="2"/>
-        <v>0.12740000000000001</v>
-      </c>
-      <c r="L7" s="2">
-        <f t="shared" si="2"/>
-        <v>0.12790000000000001</v>
-      </c>
-      <c r="M7" s="2">
-        <f t="shared" si="2"/>
-        <v>0.12559999999999999</v>
-      </c>
+      <c r="C7" s="2"/>
+      <c r="D7" s="2"/>
+      <c r="E7" s="2"/>
+      <c r="F7" s="2"/>
+      <c r="G7" s="2"/>
+      <c r="H7" s="2"/>
+      <c r="I7" s="2"/>
+      <c r="J7" s="2"/>
+      <c r="K7" s="2"/>
+      <c r="L7" s="2"/>
+      <c r="M7" s="2"/>
       <c r="N7" s="2">
-        <f t="shared" si="2"/>
-        <v>0.12659999999999999</v>
+        <v>0.14913999999999999</v>
       </c>
     </row>
   </sheetData>
